--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2512468_ELIMINGRC14FINAL_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2512468_ELIMINGRC14FINAL_PROCESSED.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.103899999999999</v>
+        <v>8.101900000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9026</v>
+        <v>6.2381</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2013</v>
+        <v>1.8638</v>
       </c>
       <c r="G2" t="n">
-        <v>1.8906</v>
+        <v>1.9265</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.2884</v>
+        <v>-1.3353</v>
       </c>
       <c r="I2" t="n">
-        <v>3.179</v>
+        <v>3.2618</v>
       </c>
       <c r="J2" t="n">
-        <v>2.8052</v>
+        <v>2.916</v>
       </c>
       <c r="K2" t="n">
-        <v>0.4399</v>
+        <v>0.4516</v>
       </c>
       <c r="L2" t="n">
-        <v>2.3654</v>
+        <v>2.4644</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.9146</v>
+        <v>-0.9893999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.7282</v>
+        <v>-1.7868</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8136</v>
+        <v>0.7974</v>
       </c>
       <c r="P2" t="n">
-        <v>2.4007</v>
+        <v>2.3368</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.4007</v>
+        <v>2.3368</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8131</v>
+        <v>0.7859</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0979</v>
+        <v>0.2695</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7151999999999999</v>
+        <v>0.5164</v>
       </c>
       <c r="V2" t="n">
-        <v>2.9994</v>
+        <v>3.0526</v>
       </c>
       <c r="W2" t="n">
-        <v>2.9994</v>
+        <v>3.0526</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.7023</v>
+        <v>5.6261</v>
       </c>
       <c r="E3" t="n">
-        <v>4.983</v>
+        <v>5.8328</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2807</v>
+        <v>-0.2066</v>
       </c>
       <c r="G3" t="n">
-        <v>3.5141</v>
+        <v>3.641</v>
       </c>
       <c r="H3" t="n">
-        <v>3.1835</v>
+        <v>3.2745</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3306</v>
+        <v>0.3665</v>
       </c>
       <c r="J3" t="n">
-        <v>6.1296</v>
+        <v>6.4383</v>
       </c>
       <c r="K3" t="n">
-        <v>5.562</v>
+        <v>5.7731</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5675</v>
+        <v>0.6651</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.6155</v>
+        <v>-2.7972</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.3786</v>
+        <v>-2.4986</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2369</v>
+        <v>-0.2986</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.2006</v>
+        <v>-2.1421</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4.2012</v>
+        <v>-4.0895</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4703</v>
+        <v>0.1846</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8045</v>
+        <v>-0.4587</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3342</v>
+        <v>0.6433</v>
       </c>
       <c r="V3" t="n">
-        <v>3.8591</v>
+        <v>3.9426</v>
       </c>
       <c r="W3" t="n">
-        <v>3.8591</v>
+        <v>3.9426</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6121</v>
+        <v>3.2158</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7721</v>
+        <v>2.4442</v>
       </c>
       <c r="F4" t="n">
-        <v>0.84</v>
+        <v>0.7717000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.0268</v>
+        <v>-0.0213</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.9866</v>
+        <v>-0.994</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9599</v>
+        <v>0.9726</v>
       </c>
       <c r="J4" t="n">
-        <v>1.0235</v>
+        <v>1.0957</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3417</v>
+        <v>0.3823</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6818</v>
+        <v>0.7134</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0503</v>
+        <v>-1.1171</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.3283</v>
+        <v>-1.3763</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2781</v>
+        <v>0.2592</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3614</v>
+        <v>0.2635</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4512</v>
+        <v>0.1274</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0898</v>
+        <v>0.1361</v>
       </c>
       <c r="V4" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,37 +799,37 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5467</v>
+        <v>1.0403</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7264</v>
+        <v>0.36</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8203</v>
+        <v>0.6803</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2225</v>
+        <v>-0.2032</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2225</v>
+        <v>-0.2032</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2417</v>
+        <v>0.2797</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2417</v>
+        <v>0.2797</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4642</v>
+        <v>-0.4829</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4642</v>
+        <v>-0.4829</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -844,28 +844,28 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7489</v>
+        <v>0.2503</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4846</v>
+        <v>0.0803</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2643</v>
+        <v>0.17</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0203</v>
+        <v>0.9932</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.0203</v>
+        <v>0.9932</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. VIDAL TEIXIDOR</t>
+          <t>J. CANAL FERRER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2673</v>
+        <v>0.8682</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3986</v>
+        <v>1.6802</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8687</v>
+        <v>-0.8121</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.4773</v>
+        <v>1.7163</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.2147</v>
+        <v>-1.1074</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7374000000000001</v>
+        <v>2.8237</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5123</v>
+        <v>2.1623</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5580000000000001</v>
+        <v>0.136</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0457</v>
+        <v>2.0263</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.965</v>
+        <v>-0.446</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.6567</v>
+        <v>-1.2434</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6917</v>
+        <v>0.7974</v>
       </c>
       <c r="P6" t="n">
-        <v>2.4007</v>
+        <v>0.9737</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R6" t="n">
-        <v>2.4007</v>
+        <v>1.9474</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2636</v>
+        <v>0.3408</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2889</v>
+        <v>-0.0674</v>
       </c>
       <c r="U6" t="n">
-        <v>1.5524</v>
+        <v>0.4082</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0803</v>
+        <v>-2.1626</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1998</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.1195</v>
+        <v>-2.7216</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. CANAL FERRER</t>
+          <t>D. VIDAL TEIXIDOR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0286</v>
+        <v>0.6781</v>
       </c>
       <c r="E7" t="n">
-        <v>1.7831</v>
+        <v>0.8296</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7544999999999999</v>
+        <v>-0.1515</v>
       </c>
       <c r="G7" t="n">
-        <v>1.7223</v>
+        <v>-2.5287</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.091</v>
+        <v>-3.294</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8133</v>
+        <v>0.7652</v>
       </c>
       <c r="J7" t="n">
-        <v>2.1015</v>
+        <v>-0.4275</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1018</v>
+        <v>-0.5413</v>
       </c>
       <c r="L7" t="n">
-        <v>1.9997</v>
+        <v>0.1139</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3791</v>
+        <v>-2.1012</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1927</v>
+        <v>-2.7526</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8136</v>
+        <v>0.6514</v>
       </c>
       <c r="P7" t="n">
-        <v>1.0003</v>
+        <v>2.3368</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0003</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0006</v>
+        <v>2.3368</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4457</v>
+        <v>0.8184</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1623</v>
+        <v>0.036</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2834</v>
+        <v>0.7824</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.1398</v>
+        <v>0.0516</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5196</v>
+        <v>1.2211</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.6593</v>
+        <v>-1.1695</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F. PALLARES ARUMI</t>
+          <t>G. SABATÉS SALA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7211</v>
+        <v>0.6079</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9913999999999999</v>
+        <v>0.6079</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2702</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8424</v>
+        <v>0.6079</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3555</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.1979</v>
+        <v>0.6079</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7869</v>
+        <v>0.6079</v>
       </c>
       <c r="K8" t="n">
-        <v>2.3411</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5542</v>
+        <v>0.6079</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.6293</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.9856</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6437</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.2003</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.2003</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.4007</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9631</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7449</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2182</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5999</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.3401</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2598</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. SABATÉS SALA</t>
+          <t>F. PALLARES ARUMI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5999</v>
+        <v>0.3108</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5999</v>
+        <v>0.6621</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>-0.3512</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5999</v>
+        <v>-0.8327</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>0.3587</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5999</v>
+        <v>-1.1913</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5999</v>
+        <v>1.9409</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>2.435</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5999</v>
+        <v>-0.494</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>-2.7736</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>-2.0763</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-0.6973</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.1684</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.1684</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.3368</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>0.5856</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.2206</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>0.365</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.6105</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.3311</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6067</v>
+        <v>-0.4252</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4649</v>
+        <v>0.4828</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0716</v>
+        <v>-0.908</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1762</v>
+        <v>0.2946</v>
       </c>
       <c r="H10" t="n">
-        <v>0.466</v>
+        <v>0.5163</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2899</v>
+        <v>-0.2217</v>
       </c>
       <c r="J10" t="n">
-        <v>2.0125</v>
+        <v>2.2511</v>
       </c>
       <c r="K10" t="n">
-        <v>2.7228</v>
+        <v>2.8584</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7104</v>
+        <v>-0.6073</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.8363</v>
+        <v>-1.9565</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.2568</v>
+        <v>-2.3421</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4205</v>
+        <v>0.3856</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6002</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.2009</v>
+        <v>-3.1158</v>
       </c>
       <c r="R10" t="n">
-        <v>2.6007</v>
+        <v>2.5316</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3369</v>
+        <v>0.4234</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4536</v>
+        <v>0.1265</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1167</v>
+        <v>0.2969</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5196</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.7194</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.9583</v>
+        <v>-1.6309</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9088000000000001</v>
+        <v>-0.5032</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0495</v>
+        <v>-1.1277</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.6353</v>
+        <v>-1.6608</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.1622</v>
+        <v>-1.1679</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4731</v>
+        <v>-0.4929</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4654</v>
+        <v>0.5628</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4235</v>
+        <v>0.4978</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0419</v>
+        <v>0.065</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.1007</v>
+        <v>-2.2236</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.5857</v>
+        <v>-1.6658</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.515</v>
+        <v>-0.5578</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="R11" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0974</v>
+        <v>0.4126</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3533</v>
+        <v>-0.1255</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4507</v>
+        <v>0.5381</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.4204</v>
+        <v>-0.3826</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1795</v>
+        <v>0.2279</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5999</v>
+        <v>-0.6105</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.1368</v>
+        <v>-2.2225</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8867</v>
+        <v>1.2852</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.0235</v>
+        <v>-3.5076</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.7244</v>
+        <v>-2.7432</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.1284</v>
+        <v>-1.171</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.596</v>
+        <v>-1.5722</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.8305</v>
+        <v>-0.7131</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5217000000000001</v>
+        <v>0.5671</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.3522</v>
+        <v>-1.2801</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.8938</v>
+        <v>-2.0302</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.6501</v>
+        <v>-1.7381</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2438</v>
+        <v>-0.292</v>
       </c>
       <c r="P12" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="S12" t="n">
-        <v>0.587</v>
+        <v>0.5734</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4822</v>
+        <v>-0.2492</v>
       </c>
       <c r="U12" t="n">
-        <v>1.0693</v>
+        <v>0.8225</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
       <c r="W12" t="n">
-        <v>2.3995</v>
+        <v>2.4421</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.5993</v>
+        <v>-3.6632</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.2338</v>
+        <v>-3.1929</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.4511</v>
+        <v>-3.1382</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2173</v>
+        <v>-0.0547</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.1111</v>
+        <v>-1.1179</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.3004</v>
+        <v>-1.2782</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1893</v>
+        <v>0.1603</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.2745</v>
+        <v>-0.1877</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.3145</v>
+        <v>-0.2283</v>
       </c>
       <c r="L13" t="n">
-        <v>0.04</v>
+        <v>0.0405</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.8366</v>
+        <v>-0.9302</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.9859</v>
+        <v>-1.05</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1493</v>
+        <v>0.1198</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.2006</v>
+        <v>-2.1421</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.0009</v>
+        <v>-2.921</v>
       </c>
       <c r="R13" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6778</v>
+        <v>0.6777</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0955</v>
+        <v>0.0222</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7732</v>
+        <v>0.6555</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.5999</v>
+        <v>-0.6105</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.0803</v>
+        <v>-0.0516</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.5196</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>12.6463</v>
+        <v>12.9776</v>
       </c>
       <c r="E14" t="n">
-        <v>14.1488</v>
+        <v>16.7815</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.5024</v>
+        <v>-3.8036</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.136700000000001</v>
+        <v>-0.9215000000000002</v>
       </c>
       <c r="H14" t="n">
-        <v>-6.389199999999999</v>
+        <v>-6.4015</v>
       </c>
       <c r="I14" t="n">
-        <v>5.2525</v>
+        <v>5.479900000000002</v>
       </c>
       <c r="J14" t="n">
-        <v>15.5489</v>
+        <v>16.9264</v>
       </c>
       <c r="K14" t="n">
-        <v>11.8237</v>
+        <v>12.6114</v>
       </c>
       <c r="L14" t="n">
-        <v>3.7251</v>
+        <v>4.315100000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-16.6854</v>
+        <v>-17.8479</v>
       </c>
       <c r="N14" t="n">
-        <v>-18.2128</v>
+        <v>-19.0129</v>
       </c>
       <c r="O14" t="n">
-        <v>1.5274</v>
+        <v>1.1651</v>
       </c>
       <c r="P14" t="n">
-        <v>5.0014</v>
+        <v>4.868300000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>-14.004</v>
+        <v>-13.6315</v>
       </c>
       <c r="R14" t="n">
-        <v>19.0054</v>
+        <v>18.4999</v>
       </c>
       <c r="S14" t="n">
-        <v>5.101800000000001</v>
+        <v>5.3162</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5323</v>
+        <v>-0.01830000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>5.633999999999999</v>
+        <v>5.3344</v>
       </c>
       <c r="V14" t="n">
-        <v>3.679500000000001</v>
+        <v>3.7148</v>
       </c>
       <c r="W14" t="n">
-        <v>13.1361</v>
+        <v>13.5048</v>
       </c>
       <c r="X14" t="n">
-        <v>-9.4565</v>
+        <v>-9.790099999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.1275</v>
+        <v>6.1333</v>
       </c>
       <c r="E15" t="n">
-        <v>6.2006</v>
+        <v>6.4757</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0731</v>
+        <v>-0.3423</v>
       </c>
       <c r="G15" t="n">
-        <v>7.8213</v>
+        <v>7.9288</v>
       </c>
       <c r="H15" t="n">
-        <v>5.0655</v>
+        <v>5.1813</v>
       </c>
       <c r="I15" t="n">
-        <v>2.7558</v>
+        <v>2.7474</v>
       </c>
       <c r="J15" t="n">
-        <v>8.4236</v>
+        <v>8.691800000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>5.9801</v>
+        <v>6.1708</v>
       </c>
       <c r="L15" t="n">
-        <v>2.4435</v>
+        <v>2.521</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.6022999999999999</v>
+        <v>-0.763</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9146</v>
+        <v>-0.9893999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3123</v>
+        <v>0.2264</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R15" t="n">
-        <v>2.6007</v>
+        <v>2.5316</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3941</v>
+        <v>-0.4612</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4822</v>
+        <v>-0.5482</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0881</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.8998</v>
+        <v>-1.9184</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.1596</v>
+        <v>-2.1979</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.1827</v>
+        <v>4.3455</v>
       </c>
       <c r="E16" t="n">
-        <v>6.9282</v>
+        <v>6.9424</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.7456</v>
+        <v>-2.5969</v>
       </c>
       <c r="G16" t="n">
-        <v>3.4226</v>
+        <v>3.4149</v>
       </c>
       <c r="H16" t="n">
-        <v>5.0662</v>
+        <v>5.1254</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.6436</v>
+        <v>-1.7105</v>
       </c>
       <c r="J16" t="n">
-        <v>5.882</v>
+        <v>6.0989</v>
       </c>
       <c r="K16" t="n">
-        <v>7.038</v>
+        <v>7.2253</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.156</v>
+        <v>-1.1264</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.4593</v>
+        <v>-2.684</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.9718</v>
+        <v>-2.0999</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4875</v>
+        <v>-0.5841</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.4004</v>
+        <v>-1.3632</v>
       </c>
       <c r="Q16" t="n">
-        <v>-4.0011</v>
+        <v>-3.8947</v>
       </c>
       <c r="R16" t="n">
-        <v>2.6007</v>
+        <v>2.5316</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9413</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.191</v>
+        <v>-0.6534</v>
       </c>
       <c r="U16" t="n">
-        <v>1.1323</v>
+        <v>0.6435</v>
       </c>
       <c r="V16" t="n">
-        <v>2.2191</v>
+        <v>2.3037</v>
       </c>
       <c r="W16" t="n">
-        <v>5.2384</v>
+        <v>5.3916</v>
       </c>
       <c r="X16" t="n">
-        <v>-3.0193</v>
+        <v>-3.0879</v>
       </c>
     </row>
     <row r="17">
@@ -1735,31 +1735,31 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1997</v>
+        <v>1.2237</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1997</v>
+        <v>1.2237</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1.1997</v>
+        <v>1.2237</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5998</v>
+        <v>0.6158</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="J17" t="n">
-        <v>1.1997</v>
+        <v>1.2237</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5998</v>
+        <v>0.6158</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. LOZANO MASSANET</t>
+          <t>. VICENTE SABARIEGO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2137</v>
+        <v>-0.0268</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1089</v>
+        <v>-0.2726</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1048</v>
+        <v>0.2459</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.173</v>
+        <v>-0.0631</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3086</v>
+        <v>-0.4958</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1356</v>
+        <v>0.4327</v>
       </c>
       <c r="J18" t="n">
-        <v>0.02</v>
+        <v>0.1842</v>
       </c>
       <c r="K18" t="n">
-        <v>0.02</v>
+        <v>0.1437</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.0405</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.193</v>
+        <v>-0.2473</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3286</v>
+        <v>-0.6394</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1356</v>
+        <v>0.3921</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.9737</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>0.9737</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3808</v>
+        <v>-0.5711000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1289</v>
+        <v>-0.4568</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2519</v>
+        <v>-0.1142</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3401</v>
+        <v>-0.3663</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3401</v>
+        <v>-0.3663</v>
       </c>
     </row>
     <row r="19">
@@ -1887,73 +1887,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3005</v>
+        <v>-0.0268</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4002</v>
+        <v>-0.2726</v>
       </c>
       <c r="F19" t="n">
-        <v>0.09959999999999999</v>
+        <v>0.2459</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0076</v>
+        <v>-0.0631</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.446</v>
+        <v>-0.4958</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4537</v>
+        <v>0.4327</v>
       </c>
       <c r="J19" t="n">
-        <v>0.18</v>
+        <v>0.1842</v>
       </c>
       <c r="K19" t="n">
-        <v>0.14</v>
+        <v>0.1437</v>
       </c>
       <c r="L19" t="n">
-        <v>0.04</v>
+        <v>0.0405</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1723</v>
+        <v>-0.2473</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.586</v>
+        <v>-0.6394</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4137</v>
+        <v>0.3921</v>
       </c>
       <c r="P19" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9485</v>
+        <v>-0.5711000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5800999999999999</v>
+        <v>-0.4568</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3684</v>
+        <v>-0.1142</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3599</v>
+        <v>-0.3663</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3599</v>
+        <v>-0.3663</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>. VICENTE SABARIEGO</t>
+          <t>G. LOZANO MASSANET</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1965,73 +1965,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3005</v>
+        <v>-0.2086</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4002</v>
+        <v>-0.1031</v>
       </c>
       <c r="F20" t="n">
-        <v>0.09959999999999999</v>
+        <v>-0.1055</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0076</v>
+        <v>-0.1966</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.446</v>
+        <v>-0.3295</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4537</v>
+        <v>0.1329</v>
       </c>
       <c r="J20" t="n">
-        <v>0.18</v>
+        <v>0.0205</v>
       </c>
       <c r="K20" t="n">
-        <v>0.14</v>
+        <v>0.0205</v>
       </c>
       <c r="L20" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1723</v>
+        <v>-0.2171</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.586</v>
+        <v>-0.35</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4137</v>
+        <v>0.1329</v>
       </c>
       <c r="P20" t="n">
-        <v>1.0003</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.0003</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9485</v>
+        <v>-0.3431</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5800999999999999</v>
+        <v>-0.1237</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3684</v>
+        <v>-0.2194</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3599</v>
+        <v>0.3311</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.3599</v>
+        <v>0.3311</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. MANES CARRETERO</t>
+          <t>P. MULIO CAMPOS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2043,73 +2043,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5565</v>
+        <v>-0.9837</v>
       </c>
       <c r="E21" t="n">
-        <v>1.7604</v>
+        <v>-0.2155</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.3169</v>
+        <v>-0.7681</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.334</v>
+        <v>-0.8065</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5790999999999999</v>
+        <v>0.215</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7549</v>
+        <v>-1.0215</v>
       </c>
       <c r="J21" t="n">
-        <v>1.2035</v>
+        <v>0.9355</v>
       </c>
       <c r="K21" t="n">
-        <v>1.1997</v>
+        <v>0.8544</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0038</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.5375</v>
+        <v>-1.742</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.7787</v>
+        <v>-0.6394</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.7587</v>
+        <v>-1.1026</v>
       </c>
       <c r="P21" t="n">
-        <v>1.6005</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6005</v>
+        <v>0.9737</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1428</v>
+        <v>-0.4566</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4822</v>
+        <v>-0.4568</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3395</v>
+        <v>0.0002</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.6802</v>
+        <v>0.2795</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0392</v>
+        <v>0.2795</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.7194</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. MULIO CAMPOS</t>
+          <t>M. MANES CARRETERO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2121,67 +2121,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.0825</v>
+        <v>-1.071</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.439</v>
+        <v>1.7505</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6435</v>
+        <v>-2.8215</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.7481</v>
+        <v>-1.4523</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2156</v>
+        <v>-0.6513</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.9637</v>
+        <v>-0.801</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8816000000000001</v>
+        <v>1.2805</v>
       </c>
       <c r="K22" t="n">
-        <v>0.8016</v>
+        <v>1.2316</v>
       </c>
       <c r="L22" t="n">
-        <v>0.08</v>
+        <v>0.0489</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.6297</v>
+        <v>-2.7327</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.586</v>
+        <v>-1.8828</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.0437</v>
+        <v>-0.8499</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.5579</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0003</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.0003</v>
+        <v>1.5579</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5942</v>
+        <v>-0.5145</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5800999999999999</v>
+        <v>-0.6479</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0141</v>
+        <v>0.1333</v>
       </c>
       <c r="V22" t="n">
-        <v>0.2598</v>
+        <v>-0.6621</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2598</v>
+        <v>1.1179</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="23">
@@ -2199,67 +2199,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.4449</v>
+        <v>-1.9048</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.9659</v>
+        <v>-2.2287</v>
       </c>
       <c r="F23" t="n">
-        <v>0.521</v>
+        <v>0.3238</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.7553</v>
+        <v>-0.7761</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.9533</v>
+        <v>-1.9674</v>
       </c>
       <c r="I23" t="n">
-        <v>1.1979</v>
+        <v>1.1913</v>
       </c>
       <c r="J23" t="n">
-        <v>1.1891</v>
+        <v>1.3448</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0254</v>
+        <v>0.1207</v>
       </c>
       <c r="L23" t="n">
-        <v>1.1636</v>
+        <v>1.2241</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.9444</v>
+        <v>-2.1209</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.9787</v>
+        <v>-2.0881</v>
       </c>
       <c r="O23" t="n">
-        <v>0.0343</v>
+        <v>-0.0328</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.2006</v>
+        <v>-2.1421</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.0011</v>
+        <v>-3.8947</v>
       </c>
       <c r="R23" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3491</v>
+        <v>-0.8346</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.3536</v>
+        <v>-0.8998</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0045</v>
+        <v>0.0653</v>
       </c>
       <c r="V23" t="n">
-        <v>1.8601</v>
+        <v>1.8479</v>
       </c>
       <c r="W23" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X23" t="n">
-        <v>0.6604</v>
+        <v>0.6268</v>
       </c>
     </row>
     <row r="24">
@@ -2277,67 +2277,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.6082</v>
+        <v>-2.4777</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.5337</v>
+        <v>-1.4914</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0745</v>
+        <v>-0.9863</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.5884</v>
+        <v>-1.6342</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4475</v>
+        <v>0.3838</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.0359</v>
+        <v>-2.018</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.2507</v>
+        <v>-0.1173</v>
       </c>
       <c r="K24" t="n">
-        <v>1.8195</v>
+        <v>1.8679</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.0702</v>
+        <v>-1.9852</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.3377</v>
+        <v>-1.5169</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.3719</v>
+        <v>-1.4841</v>
       </c>
       <c r="O24" t="n">
-        <v>0.0343</v>
+        <v>-0.0328</v>
       </c>
       <c r="P24" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R24" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.2001</v>
+        <v>-1.003</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4822</v>
+        <v>-0.6479</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7179</v>
+        <v>-0.3551</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.0198</v>
+        <v>-0.0353</v>
       </c>
       <c r="W24" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.2196</v>
+        <v>-1.2563</v>
       </c>
     </row>
     <row r="25">
@@ -2355,64 +2355,64 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.3896</v>
+        <v>-3.1448</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.4101</v>
+        <v>-2.1935</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.9795</v>
+        <v>-0.9513</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.5328</v>
+        <v>-1.5766</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.011</v>
+        <v>-1.0253</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.5218</v>
+        <v>-0.5513</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.2181</v>
+        <v>-0.1924</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.2181</v>
+        <v>-0.1924</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.3147</v>
+        <v>-1.3842</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.7929</v>
+        <v>-0.8329</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.5218</v>
+        <v>-0.5513</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R25" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.9162</v>
+        <v>-0.6793</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4512</v>
+        <v>-0.3332</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4651</v>
+        <v>-0.3461</v>
       </c>
       <c r="V25" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="W25" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
@@ -2433,28 +2433,28 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.8396</v>
+        <v>-4.0822</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.2572</v>
+        <v>-1.1211</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.5824</v>
+        <v>-2.9611</v>
       </c>
       <c r="G26" t="n">
-        <v>0.7433999999999999</v>
+        <v>0.8263</v>
       </c>
       <c r="H26" t="n">
-        <v>0.7433999999999999</v>
+        <v>0.8263</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0.7433999999999999</v>
+        <v>0.8263</v>
       </c>
       <c r="K26" t="n">
-        <v>0.7433999999999999</v>
+        <v>0.8263</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -2469,31 +2469,31 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="Q26" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0.6768</v>
+        <v>0.371</v>
       </c>
       <c r="T26" t="n">
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>0.6768</v>
+        <v>0.371</v>
       </c>
       <c r="V26" t="n">
-        <v>-3.2592</v>
+        <v>-3.3321</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-3.2592</v>
+        <v>-3.3321</v>
       </c>
     </row>
     <row r="27">
@@ -2511,67 +2511,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-10.7204</v>
+        <v>-10.3324</v>
       </c>
       <c r="E27" t="n">
-        <v>-5.4714</v>
+        <v>-4.9626</v>
       </c>
       <c r="F27" t="n">
-        <v>-5.2491</v>
+        <v>-5.3698</v>
       </c>
       <c r="G27" t="n">
-        <v>-5.9264</v>
+        <v>-5.9669</v>
       </c>
       <c r="H27" t="n">
-        <v>-1.4509</v>
+        <v>-1.4769</v>
       </c>
       <c r="I27" t="n">
-        <v>-4.4756</v>
+        <v>-4.4901</v>
       </c>
       <c r="J27" t="n">
-        <v>-2.5684</v>
+        <v>-2.4486</v>
       </c>
       <c r="K27" t="n">
-        <v>0.0636</v>
+        <v>0.1284</v>
       </c>
       <c r="L27" t="n">
-        <v>-2.632</v>
+        <v>-2.577</v>
       </c>
       <c r="M27" t="n">
-        <v>-3.358</v>
+        <v>-3.5183</v>
       </c>
       <c r="N27" t="n">
-        <v>-1.5145</v>
+        <v>-1.6052</v>
       </c>
       <c r="O27" t="n">
-        <v>-1.8435</v>
+        <v>-1.9131</v>
       </c>
       <c r="P27" t="n">
-        <v>-1.6005</v>
+        <v>-1.5579</v>
       </c>
       <c r="Q27" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R27" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.794</v>
+        <v>-0.3655</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.9024</v>
+        <v>-0.5667</v>
       </c>
       <c r="U27" t="n">
-        <v>0.1084</v>
+        <v>0.2012</v>
       </c>
       <c r="V27" t="n">
-        <v>-2.3995</v>
+        <v>-2.4421</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>-2.3995</v>
+        <v>-2.4421</v>
       </c>
     </row>
     <row r="28">
@@ -2589,67 +2589,67 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-12.9465</v>
+        <v>-12.5563</v>
       </c>
       <c r="E28" t="n">
-        <v>1.102300000000001</v>
+        <v>3.531199999999998</v>
       </c>
       <c r="F28" t="n">
-        <v>-14.0492</v>
+        <v>-16.0872</v>
       </c>
       <c r="G28" t="n">
-        <v>1.1442</v>
+        <v>0.8583000000000016</v>
       </c>
       <c r="H28" t="n">
-        <v>5.9431</v>
+        <v>5.905599999999998</v>
       </c>
       <c r="I28" t="n">
-        <v>-4.7989</v>
+        <v>-5.0475</v>
       </c>
       <c r="J28" t="n">
-        <v>16.8657</v>
+        <v>18.0321</v>
       </c>
       <c r="K28" t="n">
-        <v>18.353</v>
+        <v>19.1567</v>
       </c>
       <c r="L28" t="n">
-        <v>-1.4874</v>
+        <v>-1.1246</v>
       </c>
       <c r="M28" t="n">
-        <v>-15.7212</v>
+        <v>-17.1737</v>
       </c>
       <c r="N28" t="n">
-        <v>-12.4097</v>
+        <v>-13.2506</v>
       </c>
       <c r="O28" t="n">
-        <v>-3.3113</v>
+        <v>-3.9231</v>
       </c>
       <c r="P28" t="n">
-        <v>-4.001</v>
+        <v>-3.8948</v>
       </c>
       <c r="Q28" t="n">
-        <v>-19.0055</v>
+        <v>-18.5001</v>
       </c>
       <c r="R28" t="n">
-        <v>15.0042</v>
+        <v>14.6053</v>
       </c>
       <c r="S28" t="n">
-        <v>-6.0502</v>
+        <v>-5.438899999999999</v>
       </c>
       <c r="T28" t="n">
-        <v>-6.214</v>
+        <v>-5.7912</v>
       </c>
       <c r="U28" t="n">
-        <v>0.1638</v>
+        <v>0.3524999999999999</v>
       </c>
       <c r="V28" t="n">
-        <v>-4.0394</v>
+        <v>-4.0809</v>
       </c>
       <c r="W28" t="n">
-        <v>9.4566</v>
+        <v>9.7902</v>
       </c>
       <c r="X28" t="n">
-        <v>-13.4959</v>
+        <v>-13.871</v>
       </c>
     </row>
   </sheetData>
